--- a/digital/public/history.xlsx
+++ b/digital/public/history.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jp4\Documents\dkcbg\digital\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61E10E67-CB7A-477E-B682-19DC895DD409}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69BFF6BD-FBE3-4845-8353-72F6BD13904B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{C39C62A5-B4CB-47E0-BCAC-A2D1BB4CF7DB}"/>
   </bookViews>
@@ -792,12 +792,6 @@
     <t>118b</t>
   </si>
   <si>
-    <t>Music Points</t>
-  </si>
-  <si>
-    <t>Songs Completed</t>
-  </si>
-  <si>
     <t>Banana Birds Returned</t>
   </si>
   <si>
@@ -856,6 +850,12 @@
   </si>
   <si>
     <t>√</t>
+  </si>
+  <si>
+    <t>Homework</t>
+  </si>
+  <si>
+    <t>Homework Completed</t>
   </si>
 </sst>
 </file>
@@ -2793,13 +2793,13 @@
         <v>0</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C7" s="18">
         <v>18</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E7" s="18">
         <v>62</v>
@@ -2811,7 +2811,7 @@
         <v>87</v>
       </c>
       <c r="H7" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -3149,13 +3149,13 @@
         <v>1</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C8" s="18">
         <v>48</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E8" s="18">
         <v>25</v>
@@ -3167,7 +3167,7 @@
         <v>27</v>
       </c>
       <c r="H8" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I8">
         <v>1</v>
@@ -3519,13 +3519,13 @@
         <v>2</v>
       </c>
       <c r="B9" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C9" s="18">
         <v>47</v>
       </c>
       <c r="D9" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E9" s="18">
         <v>12</v>
@@ -3537,7 +3537,7 @@
         <v>7</v>
       </c>
       <c r="H9" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I9">
         <v>1</v>
@@ -3896,13 +3896,13 @@
         <v>3</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C10" s="18">
         <v>63</v>
       </c>
       <c r="D10" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E10" s="18">
         <v>75</v>
@@ -3914,7 +3914,7 @@
         <v>67</v>
       </c>
       <c r="H10" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I10">
         <v>1</v>
@@ -4244,13 +4244,13 @@
         <v>4</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C11" s="18">
         <v>30</v>
       </c>
       <c r="D11" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E11" s="18">
         <v>20</v>
@@ -4262,7 +4262,7 @@
         <v>46</v>
       </c>
       <c r="H11" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I11">
         <v>1</v>
@@ -4961,13 +4961,13 @@
         <v>6</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C13" s="18">
         <v>1</v>
       </c>
       <c r="D13" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E13" s="18">
         <v>112</v>
@@ -4979,7 +4979,7 @@
         <v>108</v>
       </c>
       <c r="H13" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I13">
         <v>1</v>
@@ -5289,13 +5289,13 @@
         <v>7</v>
       </c>
       <c r="B14" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C14" s="18">
         <v>49</v>
       </c>
       <c r="D14" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E14" s="18">
         <v>21</v>
@@ -5307,7 +5307,7 @@
         <v>2</v>
       </c>
       <c r="H14" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I14">
         <v>1</v>
@@ -5635,13 +5635,13 @@
         <v>8</v>
       </c>
       <c r="B15" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C15" s="18">
         <v>37</v>
       </c>
       <c r="D15" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E15" s="18">
         <v>41</v>
@@ -5653,7 +5653,7 @@
         <v>24</v>
       </c>
       <c r="H15" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I15">
         <v>1</v>
@@ -5985,13 +5985,13 @@
         <v>9</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C16" s="18">
         <v>94</v>
       </c>
       <c r="D16" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E16" s="18">
         <v>24</v>
@@ -6003,7 +6003,7 @@
         <v>33</v>
       </c>
       <c r="H16" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I16">
         <v>1</v>
@@ -6333,13 +6333,13 @@
         <v>10</v>
       </c>
       <c r="B17" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C17" s="18">
         <v>57</v>
       </c>
       <c r="D17" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E17" s="18">
         <v>32</v>
@@ -6351,7 +6351,7 @@
         <v>50</v>
       </c>
       <c r="H17" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I17">
         <v>1</v>
@@ -7034,13 +7034,13 @@
         <v>12</v>
       </c>
       <c r="B19" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C19" s="18">
         <v>19</v>
       </c>
       <c r="D19" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E19" s="18">
         <v>15</v>
@@ -7052,7 +7052,7 @@
         <v>74</v>
       </c>
       <c r="H19" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I19">
         <v>1</v>
@@ -7380,13 +7380,13 @@
         <v>13</v>
       </c>
       <c r="B20" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C20" s="18">
         <v>108</v>
       </c>
       <c r="D20" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E20" s="18">
         <v>73</v>
@@ -7398,7 +7398,7 @@
         <v>106</v>
       </c>
       <c r="H20" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I20">
         <v>1</v>
@@ -7728,13 +7728,13 @@
         <v>14</v>
       </c>
       <c r="B21" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C21" s="18">
         <v>33</v>
       </c>
       <c r="D21" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E21" s="18">
         <v>30</v>
@@ -7746,7 +7746,7 @@
         <v>113</v>
       </c>
       <c r="H21" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I21">
         <v>1</v>
@@ -8078,13 +8078,13 @@
         <v>15</v>
       </c>
       <c r="B22" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C22" s="18">
         <v>45</v>
       </c>
       <c r="D22" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E22" s="18">
         <v>98</v>
@@ -8096,7 +8096,7 @@
         <v>78</v>
       </c>
       <c r="H22" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I22">
         <v>1</v>
@@ -8419,13 +8419,13 @@
         <v>16</v>
       </c>
       <c r="B23" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C23" s="18">
         <v>85</v>
       </c>
       <c r="D23" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E23" s="18">
         <v>53</v>
@@ -8437,7 +8437,7 @@
         <v>107</v>
       </c>
       <c r="H23" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I23">
         <v>1</v>
@@ -8767,13 +8767,13 @@
         <v>17</v>
       </c>
       <c r="B24" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C24" s="18">
         <v>42</v>
       </c>
       <c r="D24" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E24" s="18">
         <v>29</v>
@@ -8785,7 +8785,7 @@
         <v>69</v>
       </c>
       <c r="H24" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I24">
         <v>1</v>
@@ -9429,13 +9429,13 @@
         <v>19</v>
       </c>
       <c r="B26" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C26" s="18">
         <v>8</v>
       </c>
       <c r="D26" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E26" s="18">
         <v>9</v>
@@ -9447,7 +9447,7 @@
         <v>79</v>
       </c>
       <c r="H26" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I26">
         <v>1</v>
@@ -9790,13 +9790,13 @@
         <v>20</v>
       </c>
       <c r="B27" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C27" s="18">
         <v>24</v>
       </c>
       <c r="D27" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E27" s="18">
         <v>10</v>
@@ -9808,7 +9808,7 @@
         <v>14</v>
       </c>
       <c r="H27" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I27">
         <v>1</v>
@@ -10150,13 +10150,13 @@
         <v>21</v>
       </c>
       <c r="B28" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C28" s="18">
         <v>29</v>
       </c>
       <c r="D28" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E28" s="18">
         <v>49</v>
@@ -10168,7 +10168,7 @@
         <v>57</v>
       </c>
       <c r="H28" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I28">
         <v>1</v>
@@ -10485,13 +10485,13 @@
         <v>22</v>
       </c>
       <c r="B29" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C29" s="19" t="s">
         <v>253</v>
       </c>
       <c r="D29" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E29" s="18">
         <v>59</v>
@@ -10503,7 +10503,7 @@
         <v>77</v>
       </c>
       <c r="H29" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I29">
         <v>1</v>
@@ -10842,13 +10842,13 @@
         <v>23</v>
       </c>
       <c r="B30" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C30" s="18">
         <v>72</v>
       </c>
       <c r="D30" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E30" s="18">
         <v>77</v>
@@ -10860,7 +10860,7 @@
         <v>72</v>
       </c>
       <c r="H30" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I30">
         <v>1</v>
@@ -11192,13 +11192,13 @@
         <v>24</v>
       </c>
       <c r="B31" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C31" s="18">
         <v>6</v>
       </c>
       <c r="D31" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E31" s="18">
         <v>108</v>
@@ -11210,7 +11210,7 @@
         <v>95</v>
       </c>
       <c r="H31" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I31">
         <v>1</v>
@@ -11825,13 +11825,13 @@
         <v>26</v>
       </c>
       <c r="B33" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C33" s="18">
         <v>28</v>
       </c>
       <c r="D33" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E33" s="18">
         <v>18</v>
@@ -11843,7 +11843,7 @@
         <v>3</v>
       </c>
       <c r="H33" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I33">
         <v>1</v>
@@ -12161,13 +12161,13 @@
         <v>27</v>
       </c>
       <c r="B34" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C34" s="18">
         <v>71</v>
       </c>
       <c r="D34" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E34" s="18">
         <v>6</v>
@@ -12179,7 +12179,7 @@
         <v>21</v>
       </c>
       <c r="H34" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I34">
         <v>1</v>
@@ -12517,13 +12517,13 @@
         <v>28</v>
       </c>
       <c r="B35" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C35" s="18">
         <v>105</v>
       </c>
       <c r="D35" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E35" s="18">
         <v>111</v>
@@ -12535,7 +12535,7 @@
         <v>43</v>
       </c>
       <c r="H35" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I35">
         <v>1</v>
@@ -12894,13 +12894,13 @@
         <v>29</v>
       </c>
       <c r="B36" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C36" s="18">
         <v>12</v>
       </c>
       <c r="D36" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E36" s="18">
         <v>98</v>
@@ -12912,7 +12912,7 @@
         <v>86</v>
       </c>
       <c r="H36" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I36">
         <v>1</v>
@@ -13215,13 +13215,13 @@
         <v>30</v>
       </c>
       <c r="B37" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C37" s="18">
         <v>87</v>
       </c>
       <c r="D37" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E37" s="18">
         <v>104</v>
@@ -13233,7 +13233,7 @@
         <v>49</v>
       </c>
       <c r="H37" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I37">
         <v>1</v>
@@ -13586,13 +13586,13 @@
         <v>31</v>
       </c>
       <c r="B38" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C38" s="18">
         <v>46</v>
       </c>
       <c r="D38" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E38" s="18">
         <v>46</v>
@@ -13604,7 +13604,7 @@
         <v>6</v>
       </c>
       <c r="H38" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I38">
         <v>1</v>
@@ -14226,13 +14226,13 @@
         <v>33</v>
       </c>
       <c r="B40" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C40" s="18">
         <v>98</v>
       </c>
       <c r="D40" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E40" s="18">
         <v>63</v>
@@ -14244,7 +14244,7 @@
         <v>112</v>
       </c>
       <c r="H40" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I40">
         <v>1</v>
@@ -14599,13 +14599,13 @@
         <v>34</v>
       </c>
       <c r="B41" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C41" s="18">
         <v>58</v>
       </c>
       <c r="D41" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E41" s="18">
         <v>26</v>
@@ -14617,7 +14617,7 @@
         <v>34</v>
       </c>
       <c r="H41" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I41">
         <v>1</v>
@@ -14961,13 +14961,13 @@
         <v>35</v>
       </c>
       <c r="B42" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C42" s="18">
         <v>115</v>
       </c>
       <c r="D42" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E42" s="18">
         <v>116</v>
@@ -14979,7 +14979,7 @@
         <v>116</v>
       </c>
       <c r="H42" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I42">
         <v>1</v>
@@ -15300,13 +15300,13 @@
         <v>36</v>
       </c>
       <c r="B43" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C43" s="18">
         <v>23</v>
       </c>
       <c r="D43" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E43" s="18">
         <v>40</v>
@@ -15318,7 +15318,7 @@
         <v>48</v>
       </c>
       <c r="H43" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I43">
         <v>1</v>
@@ -15657,13 +15657,13 @@
         <v>37</v>
       </c>
       <c r="B44" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C44" s="18">
         <v>86</v>
       </c>
       <c r="D44" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E44" s="18">
         <v>55</v>
@@ -15675,7 +15675,7 @@
         <v>32</v>
       </c>
       <c r="H44" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I44">
         <v>1</v>
@@ -16254,22 +16254,22 @@
         <v>39</v>
       </c>
       <c r="B46" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C46" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D46" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E46" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F46" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="G46" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="H46" s="31"/>
       <c r="J46">
@@ -16597,13 +16597,13 @@
         <v>40</v>
       </c>
       <c r="B47" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C47" s="18">
         <v>74</v>
       </c>
       <c r="D47" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E47" s="18">
         <v>19</v>
@@ -16615,7 +16615,7 @@
         <v>42</v>
       </c>
       <c r="H47" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I47">
         <v>1</v>
@@ -16939,13 +16939,13 @@
         <v>41</v>
       </c>
       <c r="B48" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C48" s="18">
         <v>32</v>
       </c>
       <c r="D48" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E48" s="18">
         <v>7</v>
@@ -16957,7 +16957,7 @@
         <v>9</v>
       </c>
       <c r="H48" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I48">
         <v>1</v>
@@ -17292,13 +17292,13 @@
         <v>42</v>
       </c>
       <c r="B49" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C49" s="18">
         <v>84</v>
       </c>
       <c r="D49" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E49" s="18">
         <v>93</v>
@@ -17310,7 +17310,7 @@
         <v>80</v>
       </c>
       <c r="H49" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I49">
         <v>1</v>
@@ -17663,13 +17663,13 @@
         <v>43</v>
       </c>
       <c r="B50" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C50" s="18">
         <v>25</v>
       </c>
       <c r="D50" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E50" s="18">
         <v>8</v>
@@ -17681,7 +17681,7 @@
         <v>105</v>
       </c>
       <c r="H50" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I50">
         <v>1</v>
@@ -18027,13 +18027,13 @@
         <v>44</v>
       </c>
       <c r="B51" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C51" s="18">
         <v>73</v>
       </c>
       <c r="D51" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E51" s="18">
         <v>64</v>
@@ -18045,7 +18045,7 @@
         <v>65</v>
       </c>
       <c r="H51" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I51">
         <v>1</v>
@@ -18672,13 +18672,13 @@
         <v>46</v>
       </c>
       <c r="B53" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C53" s="18">
         <v>2</v>
       </c>
       <c r="D53" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E53" s="18">
         <v>68</v>
@@ -18690,7 +18690,7 @@
         <v>96</v>
       </c>
       <c r="H53" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I53">
         <v>1</v>
@@ -19028,13 +19028,13 @@
         <v>47</v>
       </c>
       <c r="B54" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C54" s="18">
         <v>80</v>
       </c>
       <c r="D54" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E54" s="18">
         <v>5</v>
@@ -19046,7 +19046,7 @@
         <v>47</v>
       </c>
       <c r="H54" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I54">
         <v>1</v>
@@ -19392,13 +19392,13 @@
         <v>48</v>
       </c>
       <c r="B55" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C55" s="18">
         <v>95</v>
       </c>
       <c r="D55" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E55" s="18">
         <v>35</v>
@@ -19410,7 +19410,7 @@
         <v>62</v>
       </c>
       <c r="H55" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I55">
         <v>1</v>
@@ -19713,13 +19713,13 @@
         <v>49</v>
       </c>
       <c r="B56" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C56" s="18">
         <v>54</v>
       </c>
       <c r="D56" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E56" s="18">
         <v>54</v>
@@ -19731,7 +19731,7 @@
         <v>103</v>
       </c>
       <c r="H56" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I56">
         <v>1</v>
@@ -20027,13 +20027,13 @@
         <v>50</v>
       </c>
       <c r="B57" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C57" s="18">
         <v>104</v>
       </c>
       <c r="D57" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E57" s="18">
         <v>33</v>
@@ -20045,7 +20045,7 @@
         <v>17</v>
       </c>
       <c r="H57" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I57">
         <v>1</v>
@@ -20677,13 +20677,13 @@
         <v>52</v>
       </c>
       <c r="B59" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C59" s="18">
         <v>97</v>
       </c>
       <c r="D59" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E59" s="18">
         <v>96</v>
@@ -20695,7 +20695,7 @@
         <v>26</v>
       </c>
       <c r="H59" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I59">
         <v>1</v>
@@ -21006,13 +21006,13 @@
         <v>53</v>
       </c>
       <c r="B60" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C60" s="18">
         <v>90</v>
       </c>
       <c r="D60" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E60" s="18">
         <v>101</v>
@@ -21024,7 +21024,7 @@
         <v>85</v>
       </c>
       <c r="H60" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I60">
         <v>1</v>
@@ -21351,13 +21351,13 @@
         <v>54</v>
       </c>
       <c r="B61" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C61" s="18">
         <v>13</v>
       </c>
       <c r="D61" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E61" s="18">
         <v>1</v>
@@ -21369,7 +21369,7 @@
         <v>94</v>
       </c>
       <c r="H61" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I61">
         <v>1</v>
@@ -21672,13 +21672,13 @@
         <v>55</v>
       </c>
       <c r="B62" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C62" s="18">
         <v>92</v>
       </c>
       <c r="D62" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E62" s="18">
         <v>29</v>
@@ -21690,7 +21690,7 @@
         <v>102</v>
       </c>
       <c r="H62" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I62">
         <v>1</v>
@@ -21986,13 +21986,13 @@
         <v>56</v>
       </c>
       <c r="B63" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C63" s="18">
         <v>89</v>
       </c>
       <c r="D63" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E63" s="18">
         <v>13</v>
@@ -22004,7 +22004,7 @@
         <v>36</v>
       </c>
       <c r="H63" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I63">
         <v>1</v>
@@ -22319,13 +22319,13 @@
         <v>57</v>
       </c>
       <c r="B64" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C64" s="18">
         <v>14</v>
       </c>
       <c r="D64" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E64" s="18">
         <v>17</v>
@@ -22337,7 +22337,7 @@
         <v>38</v>
       </c>
       <c r="H64" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I64">
         <v>1</v>
@@ -22989,13 +22989,13 @@
         <v>59</v>
       </c>
       <c r="B66" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C66" s="18">
         <v>99</v>
       </c>
       <c r="D66" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E66" s="18">
         <v>119</v>
@@ -23007,7 +23007,7 @@
         <v>117</v>
       </c>
       <c r="H66" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I66">
         <v>1</v>
@@ -23346,13 +23346,13 @@
         <v>60</v>
       </c>
       <c r="B67" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C67" s="18">
         <v>112</v>
       </c>
       <c r="D67" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E67" s="18">
         <v>109</v>
@@ -23364,7 +23364,7 @@
         <v>23</v>
       </c>
       <c r="H67" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I67">
         <v>1</v>
@@ -23680,13 +23680,13 @@
         <v>61</v>
       </c>
       <c r="B68" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C68" s="18">
         <v>44</v>
       </c>
       <c r="D68" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E68" s="18">
         <v>70</v>
@@ -23698,7 +23698,7 @@
         <v>75</v>
       </c>
       <c r="H68" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I68">
         <v>1</v>
@@ -24037,13 +24037,13 @@
         <v>62</v>
       </c>
       <c r="B69" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C69" s="18">
         <v>118</v>
       </c>
       <c r="D69" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E69" s="18">
         <v>36</v>
@@ -24055,7 +24055,7 @@
         <v>101</v>
       </c>
       <c r="H69" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I69">
         <v>1</v>
@@ -24379,13 +24379,13 @@
         <v>63</v>
       </c>
       <c r="B70" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C70" s="18">
         <v>117</v>
       </c>
       <c r="D70" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E70" s="18">
         <v>117</v>
@@ -24397,7 +24397,7 @@
         <v>51</v>
       </c>
       <c r="H70" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I70">
         <v>1</v>
@@ -24741,13 +24741,13 @@
         <v>64</v>
       </c>
       <c r="B71" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C71" s="18">
         <v>9</v>
       </c>
       <c r="D71" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E71" s="18">
         <v>67</v>
@@ -24759,7 +24759,7 @@
         <v>54</v>
       </c>
       <c r="H71" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I71">
         <v>1</v>
@@ -25359,13 +25359,13 @@
         <v>66</v>
       </c>
       <c r="B73" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C73" s="18">
         <v>36</v>
       </c>
       <c r="D73" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E73" s="18">
         <v>99</v>
@@ -25377,7 +25377,7 @@
         <v>20</v>
       </c>
       <c r="H73" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I73">
         <v>1</v>
@@ -25694,13 +25694,13 @@
         <v>67</v>
       </c>
       <c r="B74" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C74" s="18">
         <v>110</v>
       </c>
       <c r="D74" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E74" s="18">
         <v>103</v>
@@ -25712,7 +25712,7 @@
         <v>25</v>
       </c>
       <c r="H74" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I74">
         <v>1</v>
@@ -26024,13 +26024,13 @@
         <v>68</v>
       </c>
       <c r="B75" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C75" s="18">
         <v>16</v>
       </c>
       <c r="D75" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E75" s="18">
         <v>115</v>
@@ -26042,7 +26042,7 @@
         <v>110</v>
       </c>
       <c r="H75" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I75">
         <v>1</v>
@@ -26372,13 +26372,13 @@
         <v>69</v>
       </c>
       <c r="B76" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C76" s="18">
         <v>41</v>
       </c>
       <c r="D76" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E76" s="18">
         <v>91</v>
@@ -26390,7 +26390,7 @@
         <v>40</v>
       </c>
       <c r="H76" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I76">
         <v>1</v>
@@ -26693,13 +26693,13 @@
         <v>70</v>
       </c>
       <c r="B77" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C77" s="18">
         <v>75</v>
       </c>
       <c r="D77" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E77" s="18">
         <v>102</v>
@@ -26711,7 +26711,7 @@
         <v>60</v>
       </c>
       <c r="H77" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I77">
         <v>1</v>
@@ -27368,13 +27368,13 @@
         <v>72</v>
       </c>
       <c r="B79" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C79" s="18">
         <v>3</v>
       </c>
       <c r="D79" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E79" s="18">
         <v>60</v>
@@ -27386,7 +27386,7 @@
         <v>29</v>
       </c>
       <c r="H79" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I79">
         <v>1</v>
@@ -27732,13 +27732,13 @@
         <v>73</v>
       </c>
       <c r="B80" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C80" s="18">
         <v>103</v>
       </c>
       <c r="D80" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E80" s="18">
         <v>57</v>
@@ -27750,7 +27750,7 @@
         <v>81</v>
       </c>
       <c r="H80" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I80">
         <v>1</v>
@@ -28079,13 +28079,13 @@
         <v>74</v>
       </c>
       <c r="B81" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C81" s="18">
         <v>68</v>
       </c>
       <c r="D81" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E81" s="18">
         <v>11</v>
@@ -28097,7 +28097,7 @@
         <v>71</v>
       </c>
       <c r="H81" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I81">
         <v>1</v>
@@ -28435,13 +28435,13 @@
         <v>75</v>
       </c>
       <c r="B82" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C82" s="18">
         <v>116</v>
       </c>
       <c r="D82" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E82" s="18">
         <v>99</v>
@@ -28453,7 +28453,7 @@
         <v>109</v>
       </c>
       <c r="H82" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I82">
         <v>1</v>
@@ -28769,13 +28769,13 @@
         <v>76</v>
       </c>
       <c r="B83" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C83" s="18">
         <v>43</v>
       </c>
       <c r="D83" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E83" s="18">
         <v>89</v>
@@ -28787,7 +28787,7 @@
         <v>18</v>
       </c>
       <c r="H83" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I83">
         <v>1</v>
@@ -29108,13 +29108,13 @@
         <v>77</v>
       </c>
       <c r="B84" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C84" s="18">
         <v>15</v>
       </c>
       <c r="D84" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E84" s="18">
         <v>13</v>
@@ -29126,7 +29126,7 @@
         <v>55</v>
       </c>
       <c r="H84" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I84">
         <v>1</v>
@@ -29748,13 +29748,13 @@
         <v>79</v>
       </c>
       <c r="B86" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C86" s="18">
         <v>10</v>
       </c>
       <c r="D86" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E86" s="18">
         <v>28</v>
@@ -29766,7 +29766,7 @@
         <v>59</v>
       </c>
       <c r="H86" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I86">
         <v>1</v>
@@ -30389,13 +30389,13 @@
         <v>81</v>
       </c>
       <c r="B88" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C88" s="18">
         <v>4</v>
       </c>
       <c r="D88" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E88" s="18">
         <v>95</v>
@@ -30407,7 +30407,7 @@
         <v>53</v>
       </c>
       <c r="H88" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I88">
         <v>1</v>
@@ -30752,13 +30752,13 @@
         <v>82</v>
       </c>
       <c r="B89" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C89" s="18">
         <v>7</v>
       </c>
       <c r="D89" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E89" s="18">
         <v>66</v>
@@ -30770,7 +30770,7 @@
         <v>19</v>
       </c>
       <c r="H89" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I89">
         <v>1</v>
@@ -31106,13 +31106,13 @@
         <v>83</v>
       </c>
       <c r="B90" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C90" s="18">
         <v>35</v>
       </c>
       <c r="D90" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E90" s="18">
         <v>74</v>
@@ -31124,7 +31124,7 @@
         <v>56</v>
       </c>
       <c r="H90" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I90">
         <v>1</v>
@@ -31446,13 +31446,13 @@
         <v>84</v>
       </c>
       <c r="B91" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C91" s="18">
         <v>40</v>
       </c>
       <c r="D91" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E91" s="18">
         <v>38</v>
@@ -31464,7 +31464,7 @@
         <v>28</v>
       </c>
       <c r="H91" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I91">
         <v>1</v>
@@ -31786,13 +31786,13 @@
         <v>85</v>
       </c>
       <c r="B92" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C92" s="18">
         <v>78</v>
       </c>
       <c r="D92" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E92" s="18">
         <v>83</v>
@@ -31804,7 +31804,7 @@
         <v>45</v>
       </c>
       <c r="H92" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I92">
         <v>1</v>
@@ -32099,18 +32099,18 @@
         <v>86</v>
       </c>
       <c r="B93" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C93" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D93" s="31"/>
       <c r="E93" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F93" s="19"/>
       <c r="G93" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="H93" s="31"/>
       <c r="J93">
@@ -32394,13 +32394,13 @@
         <v>87</v>
       </c>
       <c r="B94" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C94" s="18">
         <v>81</v>
       </c>
       <c r="D94" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E94" s="18">
         <v>3</v>
@@ -32412,7 +32412,7 @@
         <v>22</v>
       </c>
       <c r="H94" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I94">
         <v>1</v>
@@ -32736,13 +32736,13 @@
         <v>88</v>
       </c>
       <c r="B95" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C95" s="18">
         <v>100</v>
       </c>
       <c r="D95" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E95" s="18">
         <v>24</v>
@@ -32754,7 +32754,7 @@
         <v>117</v>
       </c>
       <c r="H95" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I95">
         <v>1</v>
@@ -33069,13 +33069,13 @@
         <v>89</v>
       </c>
       <c r="B96" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C96" s="18">
         <v>66</v>
       </c>
       <c r="D96" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E96" s="18">
         <v>22</v>
@@ -33087,7 +33087,7 @@
         <v>10</v>
       </c>
       <c r="H96" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I96">
         <v>1</v>
@@ -33425,13 +33425,13 @@
         <v>90</v>
       </c>
       <c r="B97" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C97" s="18">
         <v>88</v>
       </c>
       <c r="D97" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E97" s="18">
         <v>10</v>
@@ -33443,7 +33443,7 @@
         <v>104</v>
       </c>
       <c r="H97" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I97">
         <v>1</v>
@@ -33780,13 +33780,13 @@
         <v>91</v>
       </c>
       <c r="B98" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C98" s="18">
         <v>69</v>
       </c>
       <c r="D98" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E98" s="18">
         <v>107</v>
@@ -33798,7 +33798,7 @@
         <v>98</v>
       </c>
       <c r="H98" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I98">
         <v>1</v>
@@ -34456,13 +34456,13 @@
         <v>93</v>
       </c>
       <c r="B100" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C100" s="18">
         <v>114</v>
       </c>
       <c r="D100" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E100" s="18">
         <v>61</v>
@@ -34474,7 +34474,7 @@
         <v>61</v>
       </c>
       <c r="H100" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I100">
         <v>1</v>
@@ -34790,13 +34790,13 @@
         <v>94</v>
       </c>
       <c r="B101" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C101" s="18">
         <v>67</v>
       </c>
       <c r="D101" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E101" s="18">
         <v>23</v>
@@ -34808,7 +34808,7 @@
         <v>82</v>
       </c>
       <c r="H101" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I101">
         <v>1</v>
@@ -35153,13 +35153,13 @@
         <v>95</v>
       </c>
       <c r="B102" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C102" s="18">
         <v>111</v>
       </c>
       <c r="D102" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E102" s="18">
         <v>105</v>
@@ -35171,7 +35171,7 @@
         <v>114</v>
       </c>
       <c r="H102" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I102">
         <v>1</v>
@@ -35472,13 +35472,13 @@
         <v>96</v>
       </c>
       <c r="B103" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C103" s="18">
         <v>34</v>
       </c>
       <c r="D103" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E103" s="18">
         <v>14</v>
@@ -35490,7 +35490,7 @@
         <v>73</v>
       </c>
       <c r="H103" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I103">
         <v>1</v>
@@ -35819,13 +35819,13 @@
         <v>97</v>
       </c>
       <c r="B104" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C104" s="18">
         <v>106</v>
       </c>
       <c r="D104" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E104" s="18">
         <v>81</v>
@@ -35837,7 +35837,7 @@
         <v>52</v>
       </c>
       <c r="H104" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I104">
         <v>1</v>
@@ -36421,13 +36421,13 @@
         <v>99</v>
       </c>
       <c r="B106" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C106" s="18">
         <v>107</v>
       </c>
       <c r="D106" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E106" s="18">
         <v>73</v>
@@ -36439,7 +36439,7 @@
         <v>91</v>
       </c>
       <c r="H106" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I106">
         <v>1</v>
@@ -36755,13 +36755,13 @@
         <v>100</v>
       </c>
       <c r="B107" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C107" s="18">
         <v>109</v>
       </c>
       <c r="D107" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E107" s="18">
         <v>110</v>
@@ -36773,7 +36773,7 @@
         <v>115</v>
       </c>
       <c r="H107" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I107">
         <v>1</v>
@@ -37094,13 +37094,13 @@
         <v>101</v>
       </c>
       <c r="B108" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C108" s="18">
         <v>79</v>
       </c>
       <c r="D108" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E108" s="18">
         <v>45</v>
@@ -37112,7 +37112,7 @@
         <v>83</v>
       </c>
       <c r="H108" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I108">
         <v>1</v>
@@ -37465,13 +37465,13 @@
         <v>102</v>
       </c>
       <c r="B109" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C109" s="18">
         <v>64</v>
       </c>
       <c r="D109" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E109" s="18">
         <v>48</v>
@@ -37483,7 +37483,7 @@
         <v>90</v>
       </c>
       <c r="H109" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I109">
         <v>1</v>
@@ -37813,13 +37813,13 @@
         <v>103</v>
       </c>
       <c r="B110" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C110" s="18">
         <v>70</v>
       </c>
       <c r="D110" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E110" s="18">
         <v>95</v>
@@ -37831,7 +37831,7 @@
         <v>15</v>
       </c>
       <c r="H110" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I110">
         <v>1</v>
@@ -38499,13 +38499,13 @@
         <v>105</v>
       </c>
       <c r="B112" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C112" s="18">
         <v>11</v>
       </c>
       <c r="D112" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E112" s="18">
         <v>34</v>
@@ -38517,7 +38517,7 @@
         <v>37</v>
       </c>
       <c r="H112" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I112">
         <v>1</v>
@@ -38840,13 +38840,13 @@
         <v>106</v>
       </c>
       <c r="B113" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C113" s="18">
         <v>56</v>
       </c>
       <c r="D113" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E113" s="18">
         <v>35</v>
@@ -38858,7 +38858,7 @@
         <v>4</v>
       </c>
       <c r="H113" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I113">
         <v>1</v>
@@ -39174,13 +39174,13 @@
         <v>107</v>
       </c>
       <c r="B114" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C114" s="19" t="s">
         <v>254</v>
       </c>
       <c r="D114" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E114" s="18">
         <v>74</v>
@@ -39192,7 +39192,7 @@
         <v>93</v>
       </c>
       <c r="H114" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I114">
         <v>1</v>
@@ -39517,13 +39517,13 @@
         <v>108</v>
       </c>
       <c r="B115" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C115" s="18">
         <v>65</v>
       </c>
       <c r="D115" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E115" s="18">
         <v>51</v>
@@ -39535,7 +39535,7 @@
         <v>92</v>
       </c>
       <c r="H115" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I115">
         <v>1</v>
@@ -39872,13 +39872,13 @@
         <v>109</v>
       </c>
       <c r="B116" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C116" s="18">
         <v>31</v>
       </c>
       <c r="D116" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E116" s="18">
         <v>52</v>
@@ -39890,7 +39890,7 @@
         <v>31</v>
       </c>
       <c r="H116" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I116">
         <v>1</v>
@@ -40525,13 +40525,13 @@
         <v>111</v>
       </c>
       <c r="B118" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C118" s="18">
         <v>27</v>
       </c>
       <c r="D118" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E118" s="18">
         <v>42</v>
@@ -40543,7 +40543,7 @@
         <v>44</v>
       </c>
       <c r="H118" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I118">
         <v>1</v>
@@ -40864,13 +40864,13 @@
         <v>112</v>
       </c>
       <c r="B119" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C119" s="18">
         <v>17</v>
       </c>
       <c r="D119" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E119" s="18">
         <v>100</v>
@@ -40882,7 +40882,7 @@
         <v>64</v>
       </c>
       <c r="H119" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I119">
         <v>1</v>
@@ -41212,13 +41212,13 @@
         <v>113</v>
       </c>
       <c r="B120" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C120" s="18">
         <v>96</v>
       </c>
       <c r="D120" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E120" s="18">
         <v>84</v>
@@ -41230,7 +41230,7 @@
         <v>89</v>
       </c>
       <c r="H120" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I120">
         <v>1</v>
@@ -41568,13 +41568,13 @@
         <v>114</v>
       </c>
       <c r="B121" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C121" s="18">
         <v>52</v>
       </c>
       <c r="D121" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E121" s="18">
         <v>86</v>
@@ -41586,7 +41586,7 @@
         <v>99</v>
       </c>
       <c r="H121" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I121">
         <v>1</v>
@@ -41917,13 +41917,13 @@
         <v>115</v>
       </c>
       <c r="B122" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C122" s="18">
         <v>102</v>
       </c>
       <c r="D122" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E122" s="18">
         <v>76</v>
@@ -41935,7 +41935,7 @@
         <v>13</v>
       </c>
       <c r="H122" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I122">
         <v>1</v>
@@ -42565,13 +42565,13 @@
         <v>117</v>
       </c>
       <c r="B124" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C124" s="18">
         <v>26</v>
       </c>
       <c r="D124" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E124" s="18">
         <v>71</v>
@@ -42583,7 +42583,7 @@
         <v>1</v>
       </c>
       <c r="H124" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I124">
         <v>1</v>
@@ -42899,13 +42899,13 @@
         <v>118</v>
       </c>
       <c r="B125" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C125" s="18">
         <v>5</v>
       </c>
       <c r="D125" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E125" s="18">
         <v>50</v>
@@ -42917,7 +42917,7 @@
         <v>16</v>
       </c>
       <c r="H125" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I125">
         <v>1</v>
@@ -43229,13 +43229,13 @@
         <v>119</v>
       </c>
       <c r="B126" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C126" s="18">
         <v>50</v>
       </c>
       <c r="D126" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E126" s="18">
         <v>16</v>
@@ -43247,7 +43247,7 @@
         <v>76</v>
       </c>
       <c r="H126" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I126">
         <v>1</v>
@@ -43578,13 +43578,13 @@
         <v>120</v>
       </c>
       <c r="B127" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C127" s="18">
         <v>83</v>
       </c>
       <c r="D127" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E127" s="18">
         <v>113</v>
@@ -43596,7 +43596,7 @@
         <v>30</v>
       </c>
       <c r="H127" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I127">
         <v>1</v>
@@ -43907,13 +43907,13 @@
         <v>121</v>
       </c>
       <c r="B128" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C128" s="18">
         <v>101</v>
       </c>
       <c r="D128" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E128" s="18">
         <v>92</v>
@@ -43925,7 +43925,7 @@
         <v>84</v>
       </c>
       <c r="H128" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I128">
         <v>1</v>
@@ -44573,13 +44573,13 @@
         <v>123</v>
       </c>
       <c r="B130" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C130" s="18">
         <v>55</v>
       </c>
       <c r="D130" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E130" s="18">
         <v>87</v>
@@ -44591,7 +44591,7 @@
         <v>70</v>
       </c>
       <c r="H130" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I130">
         <v>1</v>
@@ -44936,13 +44936,13 @@
         <v>124</v>
       </c>
       <c r="B131" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C131" s="18">
         <v>62</v>
       </c>
       <c r="D131" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E131" s="18">
         <v>79</v>
@@ -44954,7 +44954,7 @@
         <v>39</v>
       </c>
       <c r="H131" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I131">
         <v>1</v>
@@ -45272,13 +45272,13 @@
         <v>125</v>
       </c>
       <c r="B132" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C132" s="18">
         <v>38</v>
       </c>
       <c r="D132" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E132" s="18">
         <v>72</v>
@@ -45290,7 +45290,7 @@
         <v>35</v>
       </c>
       <c r="H132" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I132">
         <v>1</v>
@@ -45605,13 +45605,13 @@
         <v>126</v>
       </c>
       <c r="B133" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C133" s="18">
         <v>76</v>
       </c>
       <c r="D133" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E133" s="18">
         <v>44</v>
@@ -45623,7 +45623,7 @@
         <v>11</v>
       </c>
       <c r="H133" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I133">
         <v>1</v>
@@ -45951,13 +45951,13 @@
         <v>127</v>
       </c>
       <c r="B134" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C134" s="18">
         <v>113</v>
       </c>
       <c r="D134" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E134" s="18">
         <v>56</v>
@@ -45969,7 +45969,7 @@
         <v>58</v>
       </c>
       <c r="H134" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I134">
         <v>1</v>
@@ -46313,13 +46313,13 @@
         <v>128</v>
       </c>
       <c r="B135" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C135" s="18">
         <v>60</v>
       </c>
       <c r="D135" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E135" s="18">
         <v>47</v>
@@ -46331,7 +46331,7 @@
         <v>41</v>
       </c>
       <c r="H135" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I135">
         <v>1</v>
@@ -46948,13 +46948,13 @@
         <v>130</v>
       </c>
       <c r="B137" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C137" s="18">
         <v>82</v>
       </c>
       <c r="D137" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E137" s="18">
         <v>80</v>
@@ -46966,7 +46966,7 @@
         <v>5</v>
       </c>
       <c r="H137" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I137">
         <v>1</v>
@@ -47269,13 +47269,13 @@
         <v>131</v>
       </c>
       <c r="B138" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C138" s="18">
         <v>91</v>
       </c>
       <c r="D138" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E138" s="18">
         <v>32</v>
@@ -47287,7 +47287,7 @@
         <v>12</v>
       </c>
       <c r="H138" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I138">
         <v>1</v>
@@ -47595,13 +47595,13 @@
         <v>132</v>
       </c>
       <c r="B139" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C139" s="18">
         <v>59</v>
       </c>
       <c r="D139" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E139" s="18">
         <v>69</v>
@@ -47613,7 +47613,7 @@
         <v>68</v>
       </c>
       <c r="H139" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I139">
         <v>1</v>
@@ -47928,13 +47928,13 @@
         <v>133</v>
       </c>
       <c r="B140" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C140" s="18">
         <v>61</v>
       </c>
       <c r="D140" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E140" s="18">
         <v>28</v>
@@ -47946,7 +47946,7 @@
         <v>66</v>
       </c>
       <c r="H140" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I140">
         <v>1</v>
@@ -48293,13 +48293,13 @@
         <v>134</v>
       </c>
       <c r="B141" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C141" s="18">
         <v>22</v>
       </c>
       <c r="D141" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E141" s="18">
         <v>69</v>
@@ -48311,7 +48311,7 @@
         <v>8</v>
       </c>
       <c r="H141" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I141">
         <v>1</v>
@@ -48951,13 +48951,13 @@
         <v>136</v>
       </c>
       <c r="B143" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C143" s="18">
         <v>22</v>
       </c>
       <c r="D143" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E143" s="18">
         <v>114</v>
@@ -48969,7 +48969,7 @@
         <v>111</v>
       </c>
       <c r="H143" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I143">
         <v>1</v>
@@ -49272,13 +49272,13 @@
         <v>137</v>
       </c>
       <c r="B144" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C144" s="18">
         <v>51</v>
       </c>
       <c r="D144" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E144" s="18">
         <v>2</v>
@@ -49290,7 +49290,7 @@
         <v>100</v>
       </c>
       <c r="H144" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I144">
         <v>1</v>
@@ -49585,13 +49585,13 @@
         <v>138</v>
       </c>
       <c r="B145" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C145" s="18">
         <v>77</v>
       </c>
       <c r="D145" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E145" s="18">
         <v>37</v>
@@ -49603,7 +49603,7 @@
         <v>63</v>
       </c>
       <c r="H145" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I145">
         <v>1</v>
@@ -49933,13 +49933,13 @@
         <v>139</v>
       </c>
       <c r="B146" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C146" s="18">
         <v>93</v>
       </c>
       <c r="D146" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E146" s="18">
         <v>88</v>
@@ -49951,7 +49951,7 @@
         <v>97</v>
       </c>
       <c r="H146" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I146">
         <v>1</v>
@@ -50244,13 +50244,13 @@
         <v>140</v>
       </c>
       <c r="B147" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C147" s="18">
         <v>39</v>
       </c>
       <c r="D147" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E147" s="18">
         <v>31</v>
@@ -50262,7 +50262,7 @@
         <v>88</v>
       </c>
       <c r="H147" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I147">
         <v>1</v>
@@ -50605,19 +50605,19 @@
         <v>141</v>
       </c>
       <c r="B148" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C148" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D148" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E148" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F148" s="31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="G148" s="19"/>
       <c r="J148">
@@ -56507,7 +56507,7 @@
     </row>
     <row r="219" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A219" s="24" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="AC219">
         <v>1</v>
@@ -56530,30 +56530,30 @@
     </row>
     <row r="220" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A220" s="24" t="s">
+        <v>273</v>
+      </c>
+      <c r="AC220">
+        <v>1</v>
+      </c>
+      <c r="AG220">
+        <v>1</v>
+      </c>
+      <c r="AK220">
+        <v>1</v>
+      </c>
+      <c r="AO220">
+        <v>1</v>
+      </c>
+      <c r="AS220">
+        <v>1</v>
+      </c>
+      <c r="AW220">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222" spans="1:133" x14ac:dyDescent="0.25">
+      <c r="A222" s="24" t="s">
         <v>275</v>
-      </c>
-      <c r="AC220">
-        <v>1</v>
-      </c>
-      <c r="AG220">
-        <v>1</v>
-      </c>
-      <c r="AK220">
-        <v>1</v>
-      </c>
-      <c r="AO220">
-        <v>1</v>
-      </c>
-      <c r="AS220">
-        <v>1</v>
-      </c>
-      <c r="AW220">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="222" spans="1:133" ht="21" x14ac:dyDescent="0.25">
-      <c r="A222" s="24" t="s">
-        <v>255</v>
       </c>
       <c r="BA222">
         <v>101</v>
@@ -56621,66 +56621,66 @@
     </row>
     <row r="223" spans="1:133" ht="21" x14ac:dyDescent="0.25">
       <c r="A223" s="24" t="s">
+        <v>276</v>
+      </c>
+      <c r="BA223" t="s">
+        <v>270</v>
+      </c>
+      <c r="BE223" t="s">
+        <v>269</v>
+      </c>
+      <c r="BI223" t="s">
+        <v>271</v>
+      </c>
+      <c r="BM223" t="s">
+        <v>267</v>
+      </c>
+      <c r="BQ223" t="s">
+        <v>268</v>
+      </c>
+      <c r="BU223" t="s">
+        <v>266</v>
+      </c>
+      <c r="BY223" t="s">
+        <v>263</v>
+      </c>
+      <c r="CC223" t="s">
+        <v>264</v>
+      </c>
+      <c r="CG223" t="s">
+        <v>265</v>
+      </c>
+      <c r="CO223" t="s">
+        <v>260</v>
+      </c>
+      <c r="CS223" t="s">
+        <v>261</v>
+      </c>
+      <c r="CW223" t="s">
+        <v>257</v>
+      </c>
+      <c r="DA223" t="s">
+        <v>259</v>
+      </c>
+      <c r="DE223" t="s">
+        <v>258</v>
+      </c>
+      <c r="DI223" t="s">
         <v>256</v>
       </c>
-      <c r="BA223" t="s">
-        <v>272</v>
-      </c>
-      <c r="BE223" t="s">
-        <v>271</v>
-      </c>
-      <c r="BI223" t="s">
-        <v>273</v>
-      </c>
-      <c r="BM223" t="s">
-        <v>269</v>
-      </c>
-      <c r="BQ223" t="s">
-        <v>270</v>
-      </c>
-      <c r="BU223" t="s">
-        <v>268</v>
-      </c>
-      <c r="BY223" t="s">
-        <v>265</v>
-      </c>
-      <c r="CC223" t="s">
-        <v>266</v>
-      </c>
-      <c r="CG223" t="s">
-        <v>267</v>
-      </c>
-      <c r="CO223" t="s">
+      <c r="DM223" t="s">
+        <v>256</v>
+      </c>
+      <c r="DQ223" t="s">
         <v>262</v>
       </c>
-      <c r="CS223" t="s">
-        <v>263</v>
-      </c>
-      <c r="CW223" t="s">
-        <v>259</v>
-      </c>
-      <c r="DA223" t="s">
-        <v>261</v>
-      </c>
-      <c r="DE223" t="s">
-        <v>260</v>
-      </c>
-      <c r="DI223" t="s">
-        <v>258</v>
-      </c>
-      <c r="DM223" t="s">
-        <v>258</v>
-      </c>
-      <c r="DQ223" t="s">
-        <v>264</v>
-      </c>
       <c r="DU223" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="225" spans="1:133" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A225" s="24" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="BA225">
         <v>20</v>
